--- a/model/Atelier_North_FPA_Model.xlsx
+++ b/model/Atelier_North_FPA_Model.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B7D15D-0DF1-4482-8290-FB36C8B57D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21482D26-C5E8-48A7-8410-2D4381392438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3138,15 +3138,6 @@
     <xf numFmtId="0" fontId="39" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -3194,6 +3185,15 @@
     </xf>
     <xf numFmtId="166" fontId="24" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6257,33 +6257,33 @@
       <c r="P6" s="140"/>
     </row>
     <row r="7" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="183">
+      <c r="B7" s="180">
         <f>'13W Cash Flow'!$D$45</f>
         <v>205000</v>
       </c>
-      <c r="C7" s="184"/>
-      <c r="D7" s="185"/>
+      <c r="C7" s="181"/>
+      <c r="D7" s="182"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="183">
+      <c r="F7" s="180">
         <f>'13W Cash Flow'!$D$46</f>
         <v>139650.21652399999</v>
       </c>
-      <c r="G7" s="184"/>
-      <c r="H7" s="185"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="182"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="183">
+      <c r="J7" s="180">
         <f>'13W Cash Flow'!$D$51</f>
         <v>114528.43459999998</v>
       </c>
-      <c r="K7" s="184"/>
-      <c r="L7" s="185"/>
+      <c r="K7" s="181"/>
+      <c r="L7" s="182"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="186">
+      <c r="N7" s="183">
         <f>'13W Cash Flow'!$D$56</f>
         <v>27.78054827800208</v>
       </c>
-      <c r="O7" s="187"/>
-      <c r="P7" s="188"/>
+      <c r="O7" s="184"/>
+      <c r="P7" s="185"/>
     </row>
     <row r="8" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="104" t="s">
@@ -6374,33 +6374,33 @@
       <c r="P11" s="140"/>
     </row>
     <row r="12" spans="2:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="183">
+      <c r="B12" s="180">
         <f>'13W Cash Flow'!$Q$77</f>
         <v>747630.46</v>
       </c>
-      <c r="C12" s="184"/>
-      <c r="D12" s="185"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="182"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="189">
+      <c r="F12" s="186">
         <f>'Channel Profitability'!$H$11</f>
         <v>0.59786243570743614</v>
       </c>
-      <c r="G12" s="190"/>
-      <c r="H12" s="191"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="188"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="183">
+      <c r="J12" s="180">
         <f>'Store Break-Even'!$D$28</f>
         <v>-1104.7200000000012</v>
       </c>
-      <c r="K12" s="184"/>
-      <c r="L12" s="185"/>
+      <c r="K12" s="181"/>
+      <c r="L12" s="182"/>
       <c r="M12" s="7"/>
-      <c r="N12" s="183">
+      <c r="N12" s="180">
         <f>'Store Break-Even'!$D$35</f>
         <v>-2108.2442748091562</v>
       </c>
-      <c r="O12" s="184"/>
-      <c r="P12" s="185"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="182"/>
     </row>
     <row r="13" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="104" t="s">
@@ -6465,84 +6465,84 @@
       <c r="P15" s="12"/>
     </row>
     <row r="16" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="182" t="str">
+      <c r="B16" s="179" t="str">
         <f>"Cash bottoms out at "&amp;TEXT('13W Cash Flow'!$D$51,"""S$""#,##0")&amp;" in Week "&amp;'13W Cash Flow'!$D$52&amp;IF('13W Cash Flow'!$D$54&lt;0,", which is "&amp;TEXT(-'13W Cash Flow'!$D$54,"""S$""#,##0")&amp;" below the minimum buffer in "&amp;'13W Cash Flow'!$D$55&amp;IF('13W Cash Flow'!$D$55=1," week"," weeks"),", leaving "&amp;TEXT('13W Cash Flow'!$D$54,"""S$""#,##0")&amp;" of headroom")&amp;", before recovering to "&amp;TEXT('13W Cash Flow'!$D$46,"""S$""#,##0")&amp;" by Week 13."</f>
         <v>Cash bottoms out at S$114,528 in Week 9, which is S$5,472 below the minimum buffer in 1 week, before recovering to S$139,650 by Week 13.</v>
       </c>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-      <c r="E16" s="182"/>
-      <c r="F16" s="182"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="182"/>
-      <c r="I16" s="182"/>
-      <c r="J16" s="182"/>
-      <c r="K16" s="182"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="182"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="182"/>
+      <c r="C16" s="179"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="179"/>
+      <c r="I16" s="179"/>
+      <c r="J16" s="179"/>
+      <c r="K16" s="179"/>
+      <c r="L16" s="179"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="179"/>
+      <c r="O16" s="179"/>
+      <c r="P16" s="179"/>
     </row>
     <row r="17" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="182" t="str">
+      <c r="B17" s="179" t="str">
         <f>"Inventory and supplier payments take "&amp;TEXT('13W Cash Flow'!$Q$21/'13W Cash Flow'!$Q$36,"0.0%")&amp;" of 13-week outflows "&amp;"("&amp;TEXT('13W Cash Flow'!$Q$21,"""S$""#,##0")&amp;") - the AW26 buy, not trading, is what drains the cash."</f>
         <v>Inventory and supplier payments take 52.5% of 13-week outflows (S$409,023) - the AW26 buy, not trading, is what drains the cash.</v>
       </c>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="182"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="182"/>
-      <c r="I17" s="182"/>
-      <c r="J17" s="182"/>
-      <c r="K17" s="182"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="182"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="182"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="179"/>
+      <c r="I17" s="179"/>
+      <c r="J17" s="179"/>
+      <c r="K17" s="179"/>
+      <c r="L17" s="179"/>
+      <c r="M17" s="179"/>
+      <c r="N17" s="179"/>
+      <c r="O17" s="179"/>
+      <c r="P17" s="179"/>
     </row>
     <row r="18" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="182" t="str">
+      <c r="B18" s="179" t="str">
         <f>"The flagship store trades "&amp;TEXT(ABS('Store Break-Even'!$D$36),"0.0%")&amp;IF('Store Break-Even'!$D$36&lt;0," below"," above")&amp;" break-even, but earns the highest contribution margin of any channel at "&amp;TEXT('Channel Profitability'!$D$23,"0.0%")&amp;"; e-commerce delivers the largest direct channel profit at "&amp;TEXT('Channel Profitability'!$E$34/6,"""S$""#,##0")&amp;" per month."</f>
         <v>The flagship store trades 2.5% below break-even, but earns the highest contribution margin of any channel at 52.4%; e-commerce delivers the largest direct channel profit at S$28,478 per month.</v>
       </c>
-      <c r="C18" s="182"/>
-      <c r="D18" s="182"/>
-      <c r="E18" s="182"/>
-      <c r="F18" s="182"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="182"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="182"/>
+      <c r="C18" s="179"/>
+      <c r="D18" s="179"/>
+      <c r="E18" s="179"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="179"/>
+      <c r="I18" s="179"/>
+      <c r="J18" s="179"/>
+      <c r="K18" s="179"/>
+      <c r="L18" s="179"/>
+      <c r="M18" s="179"/>
+      <c r="N18" s="179"/>
+      <c r="O18" s="179"/>
+      <c r="P18" s="179"/>
     </row>
     <row r="19" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="182" t="str">
+      <c r="B19" s="179" t="str">
         <f>"Store improvement ends Week 13 with "&amp;TEXT(Scenarios!$E$63,"""S$""#,##0")&amp;" of cash against "&amp;TEXT(Scenarios!$D$63,"""S$""#,##0")&amp;" as-is and "&amp;TEXT(Scenarios!$F$63,"""S$""#,##0")&amp;" on exit; closure needs "&amp;TEXT(Scenarios!$F$72,"0.0%")&amp;" of store demand to migrate online just to beat standing still."</f>
         <v>Store improvement ends Week 13 with S$163,302 of cash against S$139,650 as-is and S$110,579 on exit; closure needs 3.6% of store demand to migrate online just to beat standing still.</v>
       </c>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="182"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="182"/>
+      <c r="C19" s="179"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="179"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="179"/>
+      <c r="I19" s="179"/>
+      <c r="J19" s="179"/>
+      <c r="K19" s="179"/>
+      <c r="L19" s="179"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
     </row>
     <row r="20" spans="2:16" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
@@ -8746,11 +8746,11 @@
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="189" t="s">
         <v>573</v>
       </c>
-      <c r="C6" s="192"/>
-      <c r="D6" s="192"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="2:5" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8773,11 +8773,11 @@
       <c r="E8" s="7"/>
     </row>
     <row r="9" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="192" t="s">
+      <c r="B9" s="189" t="s">
         <v>576</v>
       </c>
-      <c r="C9" s="192"/>
-      <c r="D9" s="192"/>
+      <c r="C9" s="189"/>
+      <c r="D9" s="189"/>
       <c r="E9" s="7"/>
     </row>
     <row r="10" spans="2:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8800,11 +8800,11 @@
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="192" t="s">
+      <c r="B12" s="189" t="s">
         <v>579</v>
       </c>
-      <c r="C12" s="192"/>
-      <c r="D12" s="192"/>
+      <c r="C12" s="189"/>
+      <c r="D12" s="189"/>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="2:5" ht="53" customHeight="1" x14ac:dyDescent="0.35">
@@ -8829,11 +8829,11 @@
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="192" t="s">
+      <c r="B15" s="189" t="s">
         <v>580</v>
       </c>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="2:5" ht="53" customHeight="1" x14ac:dyDescent="0.35">
@@ -8856,11 +8856,11 @@
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="192" t="s">
+      <c r="B18" s="189" t="s">
         <v>583</v>
       </c>
-      <c r="C18" s="192"/>
-      <c r="D18" s="192"/>
+      <c r="C18" s="189"/>
+      <c r="D18" s="189"/>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="2:5" ht="53" customHeight="1" x14ac:dyDescent="0.35">
@@ -8883,11 +8883,11 @@
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="192" t="s">
+      <c r="B21" s="189" t="s">
         <v>586</v>
       </c>
-      <c r="C21" s="192"/>
-      <c r="D21" s="192"/>
+      <c r="C21" s="189"/>
+      <c r="D21" s="189"/>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="2:5" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8910,11 +8910,11 @@
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="192" t="s">
+      <c r="B24" s="189" t="s">
         <v>589</v>
       </c>
-      <c r="C24" s="192"/>
-      <c r="D24" s="192"/>
+      <c r="C24" s="189"/>
+      <c r="D24" s="189"/>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="2:5" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8938,11 +8938,11 @@
       <c r="E26" s="7"/>
     </row>
     <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="193" t="s">
+      <c r="B27" s="190" t="s">
         <v>591</v>
       </c>
-      <c r="C27" s="193"/>
-      <c r="D27" s="193"/>
+      <c r="C27" s="190"/>
+      <c r="D27" s="190"/>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="2:5" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -13705,25 +13705,25 @@
       </c>
     </row>
     <row r="4" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="194" t="str">
+      <c r="B4" s="191" t="str">
         <f>"Preferred scenario:  "&amp;INDEX($D$6:$F$6,MATCH(MAX($D$50:$F$50),$D$50:$F$50,0))&amp;"   ·   highest monthly run-rate operating profit at "&amp;TEXT(MAX($D$50:$F$50),"""S$""#,##0")&amp;", the strongest Week 13 cash position at "&amp;TEXT(INDEX($D$63:$F$63,MATCH(MAX($D$50:$F$50),$D$50:$F$50,0)),"""S$""#,##0")&amp;" and "&amp;INDEX($D$67:$F$67,MATCH(MAX($D$50:$F$50),$D$50:$F$50,0))&amp;IF(INDEX($D$67:$F$67,MATCH(MAX($D$50:$F$50),$D$50:$F$50,0))=1," week"," weeks")&amp;" below the minimum cash buffer."</f>
         <v>Preferred scenario:  2. Store Improvement   ·   highest monthly run-rate operating profit at S$27,343, the strongest Week 13 cash position at S$163,302 and 0 weeks below the minimum cash buffer.</v>
       </c>
-      <c r="C4" s="194"/>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="194"/>
-      <c r="G4" s="194"/>
-      <c r="H4" s="194"/>
-      <c r="I4" s="194"/>
-      <c r="J4" s="194"/>
-      <c r="K4" s="194"/>
-      <c r="L4" s="194"/>
-      <c r="M4" s="194"/>
-      <c r="N4" s="194"/>
-      <c r="O4" s="194"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="194"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="191"/>
+      <c r="M4" s="191"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="191"/>
+      <c r="P4" s="191"/>
+      <c r="Q4" s="191"/>
     </row>
     <row r="5" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="12" t="s">
@@ -15883,24 +15883,24 @@
       <c r="Q79" s="3"/>
     </row>
     <row r="80" spans="2:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="195" t="str">
+      <c r="B80" s="192" t="str">
         <f>_xlfn._LONGTEXT("Trade-off: Scenario 2 protects revenue and delivers the strongest 13-week cash position, but it depends on management actually achieving the sales and margin uplift. Scenario 3 improves the fixed-cost base permanently, yet it consumes cash first: it spend","s ")&amp;TEXT($F$67,"0")&amp;" of the 13 weeks below the minimum cash buffer and ends the quarter at "&amp;TEXT($F$63,"""S$""#,##0")&amp;", against "&amp;TEXT($E$63,"""S$""#,##0")&amp;" under improvement. On monthly run-rate profit the two are only "&amp;TEXT(ABS($E$50-$F$50),"""S$""#,##0")&amp;" apart: exit needs "&amp;TEXT($F$73,"0.0%")&amp;" of store demand to move online just to match the improvement case, against the "&amp;TEXT($F$12,"0.0%")&amp;" assumed here - so the choice turns on cash timing, execution risk and reversibility rather than on run-rate profit."</f>
         <v>Trade-off: Scenario 2 protects revenue and delivers the strongest 13-week cash position, but it depends on management actually achieving the sales and margin uplift. Scenario 3 improves the fixed-cost base permanently, yet it consumes cash first: it spends 6 of the 13 weeks below the minimum cash buffer and ends the quarter at S$110,579, against S$163,302 under improvement. On monthly run-rate profit the two are only S$255 apart: exit needs 25.8% of store demand to move online just to match the improvement case, against the 25.0% assumed here - so the choice turns on cash timing, execution risk and reversibility rather than on run-rate profit.</v>
       </c>
-      <c r="C80" s="195"/>
-      <c r="D80" s="195"/>
-      <c r="E80" s="195"/>
-      <c r="F80" s="195"/>
-      <c r="G80" s="195"/>
-      <c r="H80" s="195"/>
-      <c r="I80" s="195"/>
-      <c r="J80" s="195"/>
-      <c r="K80" s="195"/>
-      <c r="L80" s="195"/>
-      <c r="M80" s="195"/>
-      <c r="N80" s="195"/>
-      <c r="O80" s="195"/>
-      <c r="P80" s="195"/>
+      <c r="C80" s="192"/>
+      <c r="D80" s="192"/>
+      <c r="E80" s="192"/>
+      <c r="F80" s="192"/>
+      <c r="G80" s="192"/>
+      <c r="H80" s="192"/>
+      <c r="I80" s="192"/>
+      <c r="J80" s="192"/>
+      <c r="K80" s="192"/>
+      <c r="L80" s="192"/>
+      <c r="M80" s="192"/>
+      <c r="N80" s="192"/>
+      <c r="O80" s="192"/>
+      <c r="P80" s="192"/>
       <c r="Q80" s="3"/>
     </row>
     <row r="81" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23165,16 +23165,16 @@
       <c r="I61" s="3"/>
     </row>
     <row r="62" spans="2:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="195" t="s">
+      <c r="B62" s="192" t="s">
         <v>380</v>
       </c>
-      <c r="C62" s="195"/>
-      <c r="D62" s="195"/>
-      <c r="E62" s="195"/>
-      <c r="F62" s="195"/>
-      <c r="G62" s="195"/>
-      <c r="H62" s="195"/>
-      <c r="I62" s="195"/>
+      <c r="C62" s="192"/>
+      <c r="D62" s="192"/>
+      <c r="E62" s="192"/>
+      <c r="F62" s="192"/>
+      <c r="G62" s="192"/>
+      <c r="H62" s="192"/>
+      <c r="I62" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -23201,6 +23201,10 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="46" max="16383" man="1"/>
   </rowBreaks>
+  <ignoredErrors>
+    <ignoredError sqref="D9:G9" formula="1"/>
+    <ignoredError sqref="H14:H20 D21:G21 H26:H32 D33:G33" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -23285,16 +23289,16 @@
         <v>82720</v>
       </c>
       <c r="E6" s="21"/>
-      <c r="F6" s="196">
+      <c r="F6" s="193">
         <f>$D$34</f>
         <v>82720</v>
       </c>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196">
+      <c r="G6" s="193"/>
+      <c r="H6" s="193">
         <f>$D$32</f>
         <v>84828.244274809156</v>
       </c>
-      <c r="I6" s="196"/>
+      <c r="I6" s="193"/>
     </row>
     <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="25" t="s">
@@ -23354,16 +23358,16 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="196">
+      <c r="F10" s="193">
         <f>$D$35</f>
         <v>-2108.2442748091562</v>
       </c>
-      <c r="G10" s="196"/>
-      <c r="H10" s="197">
+      <c r="G10" s="193"/>
+      <c r="H10" s="194">
         <f>$D$36</f>
         <v>-2.5486512026222874E-2</v>
       </c>
-      <c r="I10" s="197"/>
+      <c r="I10" s="194"/>
     </row>
     <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="74" t="s">
@@ -23426,16 +23430,16 @@
         <v>-661.76</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="197">
+      <c r="F14" s="194">
         <f>$D$18</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="G14" s="197"/>
-      <c r="H14" s="196">
+      <c r="G14" s="194"/>
+      <c r="H14" s="193">
         <f>$D$28</f>
         <v>-1104.7200000000012</v>
       </c>
-      <c r="I14" s="196"/>
+      <c r="I14" s="193"/>
     </row>
     <row r="15" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="25" t="s">
@@ -24399,16 +24403,16 @@
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="195" t="s">
+      <c r="B72" s="192" t="s">
         <v>442</v>
       </c>
-      <c r="C72" s="195"/>
-      <c r="D72" s="195"/>
-      <c r="E72" s="195"/>
-      <c r="F72" s="195"/>
-      <c r="G72" s="195"/>
-      <c r="H72" s="195"/>
-      <c r="I72" s="195"/>
+      <c r="C72" s="192"/>
+      <c r="D72" s="192"/>
+      <c r="E72" s="192"/>
+      <c r="F72" s="192"/>
+      <c r="G72" s="192"/>
+      <c r="H72" s="192"/>
+      <c r="I72" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -27512,7 +27516,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="179" t="s">
+      <c r="B8" s="195" t="s">
         <v>602</v>
       </c>
       <c r="C8" s="154" t="s">
@@ -27538,7 +27542,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="179"/>
+      <c r="B9" s="195"/>
       <c r="C9" s="159" t="s">
         <v>604</v>
       </c>
@@ -27562,7 +27566,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="179"/>
+      <c r="B10" s="195"/>
       <c r="C10" s="159" t="s">
         <v>605</v>
       </c>
@@ -27586,7 +27590,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="179"/>
+      <c r="B11" s="195"/>
       <c r="C11" s="159" t="s">
         <v>606</v>
       </c>
@@ -27610,7 +27614,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="179"/>
+      <c r="B12" s="195"/>
       <c r="C12" s="159" t="s">
         <v>607</v>
       </c>
@@ -27634,7 +27638,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="179"/>
+      <c r="B13" s="195"/>
       <c r="C13" s="159" t="s">
         <v>608</v>
       </c>
@@ -27658,7 +27662,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="179"/>
+      <c r="B14" s="195"/>
       <c r="C14" s="159" t="s">
         <v>609</v>
       </c>
@@ -27682,7 +27686,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="179"/>
+      <c r="B15" s="195"/>
       <c r="C15" s="159" t="s">
         <v>610</v>
       </c>
@@ -27706,7 +27710,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="179"/>
+      <c r="B16" s="195"/>
       <c r="C16" s="159" t="s">
         <v>657</v>
       </c>
@@ -27730,7 +27734,7 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="179" t="s">
+      <c r="B17" s="195" t="s">
         <v>611</v>
       </c>
       <c r="C17" s="154" t="s">
@@ -27756,7 +27760,7 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="179"/>
+      <c r="B18" s="195"/>
       <c r="C18" s="159" t="s">
         <v>613</v>
       </c>
@@ -27780,7 +27784,7 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="179"/>
+      <c r="B19" s="195"/>
       <c r="C19" s="159" t="s">
         <v>614</v>
       </c>
@@ -27804,7 +27808,7 @@
       </c>
     </row>
     <row r="20" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="179"/>
+      <c r="B20" s="195"/>
       <c r="C20" s="159" t="s">
         <v>615</v>
       </c>
@@ -27828,7 +27832,7 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="179"/>
+      <c r="B21" s="195"/>
       <c r="C21" s="159" t="s">
         <v>616</v>
       </c>
@@ -27852,7 +27856,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="179"/>
+      <c r="B22" s="195"/>
       <c r="C22" s="159" t="s">
         <v>617</v>
       </c>
@@ -27876,7 +27880,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="179" t="s">
+      <c r="B23" s="195" t="s">
         <v>618</v>
       </c>
       <c r="C23" s="154" t="s">
@@ -27902,7 +27906,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="179"/>
+      <c r="B24" s="195"/>
       <c r="C24" s="159" t="s">
         <v>620</v>
       </c>
@@ -27926,7 +27930,7 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="179"/>
+      <c r="B25" s="195"/>
       <c r="C25" s="159" t="s">
         <v>621</v>
       </c>
@@ -27950,7 +27954,7 @@
       </c>
     </row>
     <row r="26" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="179" t="s">
+      <c r="B26" s="195" t="s">
         <v>622</v>
       </c>
       <c r="C26" s="154" t="s">
@@ -27976,7 +27980,7 @@
       </c>
     </row>
     <row r="27" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="179"/>
+      <c r="B27" s="195"/>
       <c r="C27" s="159" t="s">
         <v>624</v>
       </c>
@@ -28000,7 +28004,7 @@
       </c>
     </row>
     <row r="28" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="179"/>
+      <c r="B28" s="195"/>
       <c r="C28" s="159" t="s">
         <v>625</v>
       </c>
@@ -28024,7 +28028,7 @@
       </c>
     </row>
     <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="179"/>
+      <c r="B29" s="195"/>
       <c r="C29" s="159" t="s">
         <v>626</v>
       </c>
@@ -28048,7 +28052,7 @@
       </c>
     </row>
     <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="179" t="s">
+      <c r="B30" s="195" t="s">
         <v>627</v>
       </c>
       <c r="C30" s="154" t="s">
@@ -28074,7 +28078,7 @@
       </c>
     </row>
     <row r="31" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="179"/>
+      <c r="B31" s="195"/>
       <c r="C31" s="159" t="s">
         <v>629</v>
       </c>
@@ -28098,7 +28102,7 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="179"/>
+      <c r="B32" s="195"/>
       <c r="C32" s="159" t="s">
         <v>630</v>
       </c>
@@ -28122,7 +28126,7 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="179" t="s">
+      <c r="B33" s="195" t="s">
         <v>631</v>
       </c>
       <c r="C33" s="154" t="s">
@@ -28148,7 +28152,7 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="179"/>
+      <c r="B34" s="195"/>
       <c r="C34" s="159" t="s">
         <v>633</v>
       </c>
@@ -28172,7 +28176,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="179"/>
+      <c r="B35" s="195"/>
       <c r="C35" s="159" t="s">
         <v>634</v>
       </c>
@@ -28196,7 +28200,7 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="179"/>
+      <c r="B36" s="195"/>
       <c r="C36" s="159" t="s">
         <v>635</v>
       </c>
@@ -28220,7 +28224,7 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="179"/>
+      <c r="B37" s="195"/>
       <c r="C37" s="159" t="s">
         <v>658</v>
       </c>
@@ -28244,7 +28248,7 @@
       </c>
     </row>
     <row r="38" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="180" t="s">
+      <c r="B38" s="196" t="s">
         <v>664</v>
       </c>
       <c r="C38" s="159" t="s">
@@ -28270,7 +28274,7 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="181"/>
+      <c r="B39" s="197"/>
       <c r="C39" s="159" t="s">
         <v>660</v>
       </c>
@@ -28294,7 +28298,7 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="181"/>
+      <c r="B40" s="197"/>
       <c r="C40" s="159" t="s">
         <v>661</v>
       </c>
@@ -28318,7 +28322,7 @@
       </c>
     </row>
     <row r="41" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="181"/>
+      <c r="B41" s="197"/>
       <c r="C41" s="159" t="s">
         <v>662</v>
       </c>
@@ -28342,7 +28346,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="181"/>
+      <c r="B42" s="197"/>
       <c r="C42" s="159" t="s">
         <v>663</v>
       </c>
@@ -28407,5 +28411,8 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="25" max="16383" man="1"/>
   </rowBreaks>
+  <ignoredErrors>
+    <ignoredError sqref="E33:E37" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>